--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0039.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0039.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Chiến Đấu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Attack/Triển khai</t>
+          <t>Tấn Công/Triển Khai</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Hồi tưởng</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Prepare</t>
+          <t>Chuẩn bị</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sử dụng Vật phẩm</t>
+          <t>Sử dụng Vật Phẩm</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Item Wheel</t>
+          <t>Bánh xe vật phẩm</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Cửa hàng của KU-Money</t>
+          <t>Cửa hàng KU-Money</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tiếp</t>
+          <t>Tiếp theo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Slot 1</t>
+          <t>Khe 1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Slot 2</t>
+          <t>Khe 2</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Slot 3</t>
+          <t>Khe 3</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Slot 4</t>
+          <t>Khe 4</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Slot 5</t>
+          <t>Khe 5</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Slot 6</t>
+          <t>Khe 6</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Slot 7</t>
+          <t>Khe 7</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Slot 8</t>
+          <t>Khe 8</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Auto Exposure</t>
+          <t>Tự động điều chỉnh phơi sáng</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Pick Up/Put Down</t>
+          <t>Nhặt Lên/Đặt Xuống</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đặt lại</t>
+          <t>Đặt xuống</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Image Display Mode</t>
+          <t>Chế Độ Hiển Thị Hình Ảnh</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Điểm Ảo Ảnh hiện tại</t>
+          <t>Điểm Ảo Ảnh Hiện Tại</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hazard Zone Results</t>
+          <t>Kết quả Khu vực Nguy hiểm</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Rewards Respawning Waters</t>
+          <t>Phần thưởng Suối Tái Sinh</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Matrix Mimic</t>
+          <t>Bắt Chước Ma Trận</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Escalation - Tunability Breakdown</t>
+          <t>Leo Thang - Sự Cố Điều Chỉnh</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Escalation - Tune Strain Tactic</t>
+          <t>Leo Thang - Chiến Thuật Áp Lực Tần Số</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Escalation - Corrosive Flame</t>
+          <t>Bùng Nổ - Ngọn Lửa Ăn Mòn</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Escalation - Matrix Mimic I</t>
+          <t>Leo Thang - Ảo Giả Ma Trận I</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Escalation - Computation Glutton</t>
+          <t>Bùng Nổ - Kẻ Tham Tính</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Escalation - Wild Assault</t>
+          <t>Leo Thang - Tấn Công Bất Ngờ</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Escalation - Scourge of Corruption</t>
+          <t>Leo Thang - Đại Họa Ô Nhiễm</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Escalation - Echo Trooper</t>
+          <t>Bùng Nổ - Chiến Binh Tiếng Vọng</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Escalation - Matrix Mimic II</t>
+          <t>Leo Thang - Ảo Giả Ma Trận II</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Crisis Response - Pressing Advantage</t>
+          <t>Ứng Phó Khủng Hoảng - Tận Dụng Lợi Thế</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Escalation - Melting Polarity</t>
+          <t>Leo Thang - Cực Tính Tan Chảy</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Escalation - Regimented Torment</t>
+          <t>Leo Thang - Hành Quân Khắc Nghiệt</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Escalation - Sunforged Strategy</t>
+          <t>Leo Thang - Chiến Thuật Rèn Nắng</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Escalation - Intense Showdown</t>
+          <t>Bùng Nổ - Đối Đầu Nảy Lửa</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Escalation - Bulwark Protocol</t>
+          <t>Bùng Nổ - Giao Thức Phòng Ngự</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hoàn tất phục hồi</t>
+          <t>Hoàn Thành Phục Hồi</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Đến Base Camp để giao Prism Fruits</t>
+          <t>Đến Trại Cơ Bản để giao Trái Cây Lăng Kính</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Anniversary - Signature Livery</t>
+          <t>Kỷ niệm - Bộ tem chữ ký</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Bộ bao gồm</t>
+          <t>Bộ này bao gồm</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Flowers For Bạn</t>
+          <t>Những Bông Hoa Dành Tặng Em</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Nâng cấp Base Camp lên Cấp 2</t>
+          <t>Nâng cấp Trại Chính lên Cấp 2</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Nâng cấp Base Camp lên Cấp 3</t>
+          <t>Nâng cấp Trại Chính lên Cấp 3</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Nâng cấp Base Camp lên Cấp 4</t>
+          <t>Nâng cấp Trại Chính lên Cấp 4</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Nâng cấp Base Camp lên Cấp 5</t>
+          <t>Nâng cấp Trại Chính lên Cấp 5</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>S1 Stage II</t>
+          <t>Giai Đoạn II - S1</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Mô tả Generation Column</t>
+          <t>Cột Tạo Mô Tả</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Adaptive Triggers</t>
+          <t>Cơ Chế Kích Hoạt Thích Ứng</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Không required Resonator</t>
+          <t>Không có Resonator cần thiết</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Khó</t>
+          <t>Khó</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thường</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Điều chỉnh Góc để Tìm Mục tiêu</t>
+          <t>Điều chỉnh góc quay để tìm mục tiêu</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Hunt Unending</t>
+          <t>Săn không ngừng nghỉ</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Galbrena - Original Trang phục</t>
+          <t>Galbrena - Trang Phục Nguyên Bản</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Lone Drifter</t>
+          <t>Kẻ Lang Thang Cô Đơn</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Qiuyuan- Original Trang phục</t>
+          <t>Qiuyuan - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Night Flame of Black Alley</t>
+          <t>Ngọn Lửa Đêm Ở Ngõ Đen</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Giờ Phút Hy Vọng</t>
+          <t>Giờ Khắc Hy Vọng</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tái Sinh Từ Vực Thẳm</t>
+          <t>Tái Sinh Từ Vực Sâu</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Dance of Qingloong</t>
+          <t>Vũ Điệu Thanh Long</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Ảo Ảnh Viễn Xứ</t>
+          <t>Bóng Ma Viễn Xứ</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Vầng Trăng Sáng Trong Bóng Tối</t>
+          <t>Vầng Trăng Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>SkyArk Space Station: Central Sector</t>
+          <t>Trạm Không Gian SkyArk: Khu Trung Tâm</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Roya Icebreak Port</t>
+          <t>Cảng Phá Băng Roya</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Polar Nghiên cứu Outpost</t>
+          <t>Trạm Nghiên Cứu Vùng Cực</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Slumbering Exostrider</t>
+          <t>Kỵ Sĩ Ngoại Lai Ngủ Đông</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Memories of the Stars</t>
+          <t>Ký ức về những vì sao</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Startorch Academy: Auditorium</t>
+          <t>Học viện Startorch: Giảng đường</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Forever Fest</t>
+          <t>Lễ Hội Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>For Bạn Who Walk in Snow</t>
+          <t>Vì người bước đi trong tuyết</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>"A Small Workspace"</t>
+          <t>"Góc Làm Việc Nhỏ"</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Startorch Academy - Rabelle College</t>
+          <t>Học viện Startorch - Học viện Rabelle</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Academy's Dark Side</t>
+          <t>Mặt Tối Của Học Viện</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Academy's Dark Side - Classroom</t>
+          <t>Mặt Tối Của Học Viện - Lớp Học</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Academy's Dark Side - Dormitory</t>
+          <t>Mặt Tối Của Học Viện - Ký Túc Xá</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Academy's Dark Side - Vortex's Eye</t>
+          <t>Mặt Tối Của Học Viện - Mắt Xoáy</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Academy's Dark Side</t>
+          <t>Mặt Tối Của Học Viện</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Academy's Dark Side</t>
+          <t>Mặt Tối Của Học Viện</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Resolution to Illuminate the Shadows</t>
+          <t>Quyết Tâm Soi Sáng Bóng Tối</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Psychological Threshold Alternative Therapy Society</t>
+          <t>Hội Trị Liệu Ngưỡng Tâm Lý Thay Thế</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Solisia Landing</t>
+          <t>Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Twilight Woodlands</t>
+          <t>Rừng Gỗ Hoàng Hôn</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Sealed Fissure</t>
+          <t>Khe Nứt Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Silent Crag</t>
+          <t>Vách Đá Im Lìm</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Ljos Isle</t>
+          <t>Đảo Ljos</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Dimmr Deep</t>
+          <t>Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Dream's Beginning</t>
+          <t>Khởi Đầu Giấc Mơ</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chụp ảnh Studio</t>
+          <t>Phòng Chụp Ảnh</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Keystone</t>
+          <t>Đá Chìa Khóa</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Synchronization Test</t>
+          <t>Kiểm Tra Đồng Bộ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tomorrow's Horizon</t>
+          <t>Bình Minh Ngày Mai</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Reverbs From the End of Galaxies</t>
+          <t>Tiếng Vọng Từ Cõi Hư Không</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Mute khi Game chạy nền</t>
+          <t>Im lặng khi trò chơi chạy nền</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Autopilot Mode</t>
+          <t>Chế Độ Tự Lái</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Autopilot Mode</t>
+          <t>Chế Độ Tự Lái</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Applying Settings</t>
+          <t>Đang áp dụng cài đặt</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Unable to initiate page interface</t>
+          <t>Không thể khởi tạo giao diện trang</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Unable to select page interface</t>
+          <t>Không thể chọn giao diện trang</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Resonator and weapon empty</t>
+          <t>Resonator và vũ khí trống</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Random result empty</t>
+          <t>Không có kết quả ngẫu nhiên</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Selection data empty</t>
+          <t>Dữ liệu lựa chọn trống</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Selection empty</t>
+          <t>Chưa chọn gì cả</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Guaranteed pity result empty</t>
+          <t>Kết quả đảm bảo trống</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Stage data missing</t>
+          <t>Thiếu dữ liệu sân khấu.</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Weapon random result empty</t>
+          <t>Kết quả ngẫu nhiên vũ khí trống</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Random usable weapon result empty</t>
+          <t>Không có vũ khí ngẫu nhiên khả dụng</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Insufficient Enhancement Modules</t>
+          <t>Mô-đun Tăng Cường không đủ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Số lượng Enhancement Modules đã đạt tối đa</t>
+          <t>Số Mô-đun Tăng Cường đã đạt tối đa.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Unable to abandon</t>
+          <t>Không thể từ bỏ</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Insufficient selection chances</t>
+          <t>Không đủ lượt lựa chọn.</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Multi-line unsupported</t>
+          <t>Không hỗ trợ đa dòng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Please do not re-select</t>
+          <t>Xin đừng chọn lại.</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Scene modules missing</t>
+          <t>Mô-đun cảnh quan bị thiếu</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Page interface missing</t>
+          <t>Giao diện trang bị thiếu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Selection Error</t>
+          <t>Lỗi lựa chọn</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Quantity change does not exist</t>
+          <t>Sự thay đổi về số lượng không tồn tại</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Stage Error</t>
+          <t>Lỗi Giai Đoạn</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Stage Locked</t>
+          <t>Giai đoạn bị khóa</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Not yet available</t>
+          <t>Chưa khả dụng</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Chế độ Helltide không khả dụng ở giai đoạn này</t>
+          <t>Chế Độ Hắc Triều không khả dụng ở Giai Đoạn này</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Resonator này không thể sử dụng ở giai đoạn này</t>
+          <t>Resonator này không thể sử dụng trong giai đoạn này</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Vũ khí này không thể sử dụng ở giai đoạn này</t>
+          <t>Vũ khí này không thể sử dụng trong giai đoạn này.</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Resonator đã chọn không khớp với dữ liệu lưu</t>
+          <t>Cộng Hưởng Giả đã chọn không khớp với dữ liệu lưu</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Lỗi Cấp Độ Rampage</t>
+          <t>Lỗi Cấp Độ Cuồng Nộ</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Lỗi Cấp Độ Rampage</t>
+          <t>Lỗi Cấp Độ Cuồng Nộ</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Lỗi Cấp Độ Rampage</t>
+          <t>Lỗi Cấp Độ Cuồng Nộ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Not purchasable</t>
+          <t>Không thể mua</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Resonator upgrade card data missing</t>
+          <t>Thiếu dữ liệu thẻ nâng cấp Resonator</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Weapon upgrade card data missing</t>
+          <t>Thiếu dữ liệu thẻ nâng cấp vũ khí</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thẻ nâng cấp Resonator vượt quá số cấp</t>
+          <t>Số cấp thẻ nâng cấp Resonator vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thẻ nâng cấp vũ khí vượt quá số cấp</t>
+          <t>Thẻ nâng cấp vũ khí đã vượt quá cấp độ</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Refresh Failed</t>
+          <t>Làm mới thất bại</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Random result empty</t>
+          <t>Không có kết quả ngẫu nhiên</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Event data not found</t>
+          <t>Không tìm thấy dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Không times Refreshed data</t>
+          <t>Không có lần nào - Dữ liệu đã được làm mới</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Not saved</t>
+          <t>Chưa lưu</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Event data not found</t>
+          <t>Không tìm thấy dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Talent unlock data not found</t>
+          <t>Không tìm thấy dữ liệu mở khóa Tài năng</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Request exceeded max task number</t>
+          <t>Yêu cầu vượt quá số nhiệm vụ tối đa</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Task data not found</t>
+          <t>Không tìm thấy dữ liệu nhiệm vụ</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Task rewards cannot be claimed</t>
+          <t>Không thể nhận phần thưởng nhiệm vụ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Task claim repeat</t>
+          <t>Nhận nhiệm vụ lặp lại</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Không tasks to be claimed</t>
+          <t>Không có nhiệm vụ nào để nhận</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Tất cả vật phẩm có thể mua đã bị khóa, không thể làm mới</t>
+          <t>Tất cả vật phẩm có thể mua đã bị khóa, không thể làm mới.</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Chế độ Helltide khả dụng sau khi vượt qua Giai Đoạn này</t>
+          <t>Chế Độ Hắc Triều sẽ mở khóa sau khi hoàn thành Giai Đoạn này</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Please do not repeatedly claim</t>
+          <t>Xin đừng nhận đi nhận lại nhiều lần.</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa</t>
+          <t>Chưa đáp ứng đủ yêu cầu mở khóa</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nút tiền đề bị khóa</t>
+          <t>Điểm nút Điều kiện tiên quyết bị khóa</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Insufficient Knowledge Modules</t>
+          <t>Không đủ Mô-đun Tri Thức.</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Nhà sưu tập Băng ghi Lời cuối</t>
+          <t>Lahai-Roi: Người Thu Thập Cuộn Băng Lời Cuối</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Bia kỷ niệm Trở về của Soliseeds</t>
+          <t>Đài Tưởng Niệm Soliseed Trở Về</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Zani - Deluxe Trang phục</t>
+          <t>Zani - Trang phục Cao cấp</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Her Way Here</t>
+          <t>Con Đường Của Nàng Đến Đây</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Chisa - Original Trang phục</t>
+          <t>Chisa - Trang phục gốc</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Ensemble of Hunyuan</t>
+          <t>Dàn Nhạc Hunyuan</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Buling - Original Trang phục</t>
+          <t>Bộ Trang Phục Gốc - Buling</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Motorbike</t>
+          <t>Xe máy</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Workspace Quick Switch</t>
+          <t>Chuyển đổi không gian làm việc nhanh</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Synchro Shop</t>
+          <t>Cửa Hàng Đồng Bộ</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Blooming Specturm</t>
+          <t>Phổ Quang Nở Rộ</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Lynae - Original Trang phục</t>
+          <t>Lynae - Trang phục gốc</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>A Step Forward</t>
+          <t>Bước Tiến Mới</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Mornye - Original Trang phục</t>
+          <t>Chàooo - Trang phục gốc</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Trôi dạt</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Bounce Nhảy</t>
+          <t>Nhảy Nảy</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Dismount / (Giữ) Dismount Attack</t>
+          <t>Xuống xe / (Giữ) Tấn công khi xuống xe</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Return Buồng lái</t>
+          <t>Quay về buồng lái</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Discord Nest</t>
+          <t>Tổ Tacet Discord</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Echo Suite</t>
+          <t>Bộ Echo</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Projector: Geospider S4</t>
+          <t>Bộ chiếu: Geospider S4</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Projector: Zip Zap</t>
+          <t>Máy chiếu: Zip Zap</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Projector: Mining Reindeer</t>
+          <t>Máy chiếu: Mining Reindeer</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Projector: Glommoth</t>
+          <t>Máy chiếu: Glommoth</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Projector: Voidwing Moth</t>
+          <t>Máy chiếu: Voidwing Moth</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Accelerate/Forward</t>
+          <t>Tăng Tốc/Tiến Lên</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Brake/Reverse</t>
+          <t>Phanh/L?i</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Turn Left</t>
+          <t>Rẽ Trái</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Turn Right</t>
+          <t>Rẽ Phải</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Trôi dạt</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bounce Nhảy</t>
+          <t>Nhảy Nảy</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Dismount / (Giữ) Dismount Attack</t>
+          <t>Xuống xe / (Giữ) Tấn công khi xuống xe</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Front Wheel Lift</t>
+          <t>Nâng bánh trước</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Switch POV</t>
+          <t>Chuyển Góc Nhìn</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Play/Pause Music</t>
+          <t>Phát/Tạm Dừng Nhạc</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Previous Track</t>
+          <t>Bài trước</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Next Track</t>
+          <t>Bài Nhạc Tiếp Theo</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Turn Left/Right</t>
+          <t>Rẽ Trái/Phải</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Short press to dismount only</t>
+          <t>Chỉ nhấn ngắn để xuống</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Custom Keybinds</t>
+          <t>Phím Tắt Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Bộ Điều Khiển</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sustain Acceleration</t>
+          <t>Tăng Tốc Duy Trì</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Sustain Boost</t>
+          <t>Hỗ Trợ Duy Trì</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Auto-Accelerated Drift</t>
+          <t>Trượt Tự Động Tăng Tốc</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Auto-Accelerated Drift</t>
+          <t>Trượt Tự Động Tăng Tốc</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hide Motorbike HUD</t>
+          <t>Ẩn HUD Xe Máy</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅰ</t>
+          <t>Dấu chân trên vùng đất băng giá I</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅱ</t>
+          <t>Dấu chân trên vùng đất băng giá II</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅲ</t>
+          <t>Dấu chân trên vùng đất băng giá III</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅳ</t>
+          <t>Dấu chân trên vùng đất băng giá IV</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅴ</t>
+          <t>Dấu chân trên vùng đất băng giá V</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Footprints on Frostlands Ⅵ</t>
+          <t>Dấu chân trên vùng đất băng giá VI</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Tune Strain Response</t>
+          <t>Phản ứng Tune Strain</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Key already assigned</t>
+          <t>Phím đã được gán</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>(Giữ) Share Ride</t>
+          <t>(Giữ) Chia sẻ chuyến đi</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>(Giữ) Skip</t>
+          <t>(Giữ) Bỏ qua</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Dungeon process status error</t>
+          <t>Lỗi trạng thái tiến trình Tổ Tacet</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Resonator Weapon/Echo occupied</t>
+          <t>Vũ Khí/Echo Resonator Đang Bị Chiếm Dụng</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Internal error</t>
+          <t>Lỗi nội bộ</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Internal error</t>
+          <t>Lỗi nội bộ</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Resonator Weapon status abnormal</t>
+          <t>Trạng Thái Vũ Khí Resonator Bất Thường</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Resonator Echo status abnormal</t>
+          <t>Trạng Thái Echo Của Resonator Bất Thường</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Surpass 1st on the Leaderboard</t>
+          <t>Vượt qua vị trí số 1 trên Bảng Xếp Hạng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Surpass 2nd on the Leaderboard</t>
+          <t>Vượt qua vị trí thứ 2 trên Bảng Xếp Hạng</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Surpass 3rd on the Leaderboard</t>
+          <t>Vượt qua vị trí thứ 3 trên Bảng Xếp Hạng</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Failed to get scene component</t>
+          <t>Không thể lấy thành phần cảnh</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Challenge in progress</t>
+          <t>Đang thách đấu</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Not in challenge</t>
+          <t>Chưa tham gia thử thách</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Stage abnormal</t>
+          <t>Giai đoạn bất thường</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Stage configuration not found</t>
+          <t>Không tìm thấy cấu hình giai đoạn</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình chu kỳ</t>
+          <t>Không tìm thấy cấu hình Chu Kỳ</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Stage not available</t>
+          <t>Sân khấu không khả dụng.</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Đội cache empty</t>
+          <t>Bộ nhớ đội trống</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Specified team cache empty</t>
+          <t>Bộ nhớ đội hình chỉ định trống</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Rewards Điểm Phi công vượt quá tối đa</t>
+          <t>Ma trận Tốt Đôi: Điểm Phi Công - Phần Thưởng Vượt Quá Giới Hạn</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Không tìm thấy cấu hình Rewards Điểm Phi công</t>
+          <t>Không tìm thấy cấu hình phần thưởng Điểm Phi Công của Ma trận Tốt Đôi</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Rewards Điểm Phi công bị trùng lặp</t>
+          <t>Ma trận Tốt Đôi: Điểm Phi Công - Phần Thưởng Bị Trùng Lặp</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Rewards Điểm Phi công trống</t>
+          <t>Ma trận Tốt Đôi: Điểm Phi Công - Phần Thưởng Trống</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Not within cycle time range</t>
+          <t>Ngoài phạm vi chu kỳ thời gian</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Current cycle configuration not found</t>
+          <t>Không tìm thấy cấu hình chu kỳ hiện tại</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Không stage for this cycle</t>
+          <t>Không có giai đoạn nào trong chu kỳ này</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Cannot challenge across teams</t>
+          <t>Không thể khiêu chiến đội khác</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Đội limited reached</t>
+          <t>Đã đạt giới hạn thành viên trong đội.</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Resonator empty</t>
+          <t>Chưa chọn Resonator</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Resonator empty</t>
+          <t>Chưa chọn Resonator</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Max Resonator selection reached</t>
+          <t>Đã chọn đủ số Resonator tối đa</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Insufficient Resonator Vigor</t>
+          <t>Sinh lực Resonator không đủ</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Không thể lấy thông tin ghi chép đội</t>
+          <t>Không thể lấy thông tin hồ sơ đội hình</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tất cả thử thách đã hoàn thành</t>
+          <t>Hoàn thành tất cả thử thách</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>WavesLine</t>
+          <t>Đường Sóng</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Choose one picture to view</t>
+          <t>Chọn một bức ảnh để xem</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>(Giữ) Quick Build</t>
+          <t>(Giữ) Xây Dựng Nhanh</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Forever Fest</t>
+          <t>Lễ Hội Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Rover - Signature Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Khách mời lễ hội: Lynae</t>
+          <t>Khách Mời Lễ Hội: Lynae</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Khách mời lễ hội: Jiyan</t>
+          <t>Khách Mời Lễ Hội: Jiyan</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Khách mời lễ hội: Cantarella</t>
+          <t>Khách Mời Lễ Hội: Cantarella</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Khách mời lễ hội: Zani</t>
+          <t>Khách mừng lễ: Zani</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Khách mời lễ hội: Yinlin</t>
+          <t>Khách Mời Lễ Hội: Yinlin</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Startorch Motorbike</t>
+          <t>Xe Máy Sao Chổi</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Giá Trưng Bày Echo</t>
+          <t>Giá Trưng Bày Tiếng Vọng</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Wave Swing</t>
+          <t>Điệu Nhảy Sóng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Nightglow Firework</t>
+          <t>Pháo Hoa Ánh Đêm</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Philharmonic Phonograph</t>
+          <t>Đài Ghi Âm Philharmonic</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Lollo Screen</t>
+          <t>Màn hình Lollo</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Stargaze Telescope</t>
+          <t>Kính Thiên Văn Ngắm Sao</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Album Lollo Joy</t>
+          <t>Bộ Sưu Tập Niềm Vui Lollo</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Cuốn Sách Những Khoảnh Khắc</t>
+          <t>Bộ Sưu Tập Những Khoảnh Khắc</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Theo dõi Nhiệm vụ</t>
+          <t>Nhiệm vụ bản nhạc</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Hủy Tracking</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nhận Rewards</t>
+          <t>Nhận thưởng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Echoes of Silver Spring</t>
+          <t>Tiếng Vọng Suối Bạc</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Winding Corridors</t>
+          <t>Hành Lang Uốn Lượn</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Blossoms in Dreams</t>
+          <t>Hoa Trong Giấc Mộng</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Rippling Stars</t>
+          <t>Những Vì Sao Gợn Sáng</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Amber-Tinted Time</t>
+          <t>Thời Gian Ám Hổ Phách</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Whispers of Revelry</t>
+          <t>Lời thì thầm của những bữa tiệc</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>The Sea and the Swing</t>
+          <t>Biển Cả Và Chiếc Xích Đu</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tôi sẽ cho bạn xem Mech</t>
+          <t>Ta sẽ cho ngươi thấy Mech!</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Nơi mưa óng ánh rơi</t>
+          <t>Nơi Mưa Cầu Vồng Rơi</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Báo cáo thử nghiệm bổ sung năng lượng</t>
+          <t>Báo Cáo Thử Nghiệm Bổ Sung Năng Lượng</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Điều chỉnh biến môi trường</t>
+          <t>Điều chỉnh Biến số Môi trường</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tiết dopamine bất thường</t>
+          <t>Tiết Dopamine Bất Thường</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hạnh phúc tiêu chuẩn hóa</t>
+          <t>Hạnh Phúc Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Sylph lúc chạng vạng</t>
+          <t>Sylph Lúc Chạng Vạng</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Liệu pháp Waffle</t>
+          <t>Liệu Pháp Bánh Waffle</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hội chứng thiếu snack</t>
+          <t>Hội chứng thiếu đồ ăn vặt</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Suy giảm miễn dịch do thiếu snack</t>
+          <t>Thiếu Hụt Đồ Ăn Vặt</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Đơn thuốc lông tơ</t>
+          <t>Đơn Thuốc Lông Xù</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nhịp Đập Sự Sống</t>
+          <t>Nhịp Đập Sinh Mệnh</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nếp gấp trên giấy</t>
+          <t>Nếp Nhăn Trên Giấy</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Hình khắc trên mặt đất</t>
+          <t>Bản khắc Mặt đất</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Dấu vết của đôi cánh</t>
+          <t>Dấu Ấn Cánh Chim</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tinh hoa của sự tĩnh lặng</t>
+          <t>Tinh Hoa Bình Yên</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Phép thuật hạnh phúc</t>
+          <t>Phép Màu Hạnh Phúc</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>"Lễ hội không diễn lại"</t>
+          <t>"Lễ hội không bao giờ diễn lại"</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>"Hiện trường sửa chữa của Bộ Kỹ thuật"</t>
+          <t>Cảnh sửa chữa Bộ phận Kỹ thuật</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>"Cuộc sống của một Resonator"</t>
+          <t>"Cuộc đời Resonator"</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>"Cuộc sống thật tươi đẹp"</t>
+          <t>"Cuộc sống thật đẹp"</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Đến tầng cao nhất của tòa nhà Rabelle College và tìm "cô ấy"</t>
+          <t>Lên tầng cao nhất của tòa Rabelle College và tìm "cô ấy"</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Invisible Starlight</t>
+          <t>Ánh Sao Vô Hình</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Aemeath - Original Trang phục</t>
+          <t>Aemeath - Trang Phục Nguyên Bản</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Clinical Gold</t>
+          <t>Vàng Lâm Sàng</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Luuk Herssen - Original Trang phục</t>
+          <t>Luuk Herssen - Trang phục gốc</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Crimson Sky</t>
+          <t>Bầu Trời Đỏ Rực</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Exploration Aspect</t>
+          <t>Khía Cạnh Thám Hiểm</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Cosmic Spindle</t>
+          <t>Trục Xoay Vũ Trụ</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Premium Aspect</t>
+          <t>Thuộc Tính Cao Cấp</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Xác nhận / (Giữ) Điều chỉnh vị trí Resonators</t>
+          <t>Xác nhận / (Giữ) Điều chỉnh Vị trí Resonator</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Forward/Backward &amp; Turning</t>
+          <t>Tiến/Lùi &amp; Xoay người</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Không thể gán lại phím trong cảnh này</t>
+          <t>Không thể thay đổi phím tắt trong cảnh này</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Không thể gán lại phím trong cảnh này</t>
+          <t>Không thể thay đổi phím tắt trong cảnh này</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Displayed Echo updated</t>
+          <t>Đã cập nhật Echo hiển thị</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Expedition Motorbike: Glacier Track</t>
+          <t>Xe Máy Thám Hiểm: Đường Vượt Băng Giá</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Rút</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Render Distance</t>
+          <t>Khoảng Cách Kết Xuất</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Switch Sonata Effect</t>
+          <t>Chuyển Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Gold Suspended in Shadows"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Vàng Pha Bóng Tối"</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Hoàn thành Chuyện Sau "Ngọn Lửa Đỏ Rực Từ Ngày Mai"</t>
+          <t>Hoàn thành Câu Chuyện Sau "Lửa Đỏ Rực Từ Ngày Mai"</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Đạt Xếp Hạng S ở bất kỳ độ khó nào cho 12 bản nhạc trong sự kiện "Soar to the Beat"</t>
+          <t>Đạt Xếp Hạng S ở bất kỳ độ khó nào cho 12 bài trong sự kiện "Bay Theo Giai Điệu"</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Vượt qua Exam 7 trong sự kiện "Knights of the Wild"</t>
+          <t>Hoàn thành Bài Kiểm Tra 7 trong sự kiện "Hiệp Sĩ Hoang Dã"</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Hoàn thành The Sealed Gate: Easy trong sự kiện "Lahai-Roi Blocks"</t>
+          <t>Hoàn thành "Cổng Bị Phong Ấn: Dễ" trong sự kiện "Lahai-Roi Bị Phong Tỏa"</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Ashinohara's "Lady Miko"</t>
+          <t>Miko Quý Tộc của Ashinohara</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Được Giải Cứu</t>
+          <t>Nhà Nghiên Cứu Được Cứu</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Miko Ma Yêu Phim</t>
+          <t>Miko Yêu Phim Ảo Mộng</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Soliskin Và Người Mysterious Friend</t>
+          <t>Soliskin và Người Bạn Bí Ẩn</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Next task unlocks in:</t>
+          <t>Nhiệm vụ tiếp theo mở khóa trong:</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Thỏ phản chiếu trong Bóng tối</t>
+          <t>Rabbit Phản Chiếu Trong Kính</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Chương III Act IV</t>
+          <t>Chương III Hồi IV</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>True Name Illuminated</t>
+          <t>Chân Danh Hiển Lộ</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>As Heavy as Gold</t>
+          <t>Nặng Như Vàng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>The Azure Echoes</t>
+          <t>Những Âm Thanh Xanh</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Girls at the Celebration</t>
+          <t>Những Cô Gái Tại Buổi Lễ</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Shadows in Chase</t>
+          <t>Bóng Tối Đuổi Theo</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Lahai-Roi Chương III: Gold Suspended in Shadows</t>
+          <t>Chương III Lahai-Roi: Vàng Lơ Lửng Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue I</t>
+          <t>Nhật Ký Hành Trình Dimmr I</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue II</t>
+          <t>Nhật Ký Hành Trình Dimmr II</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue III</t>
+          <t>Nhật Ký Hành Trình Dimmr III</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue IV</t>
+          <t>Nhật Ký Hành Trình Dimmr IV</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue V</t>
+          <t>Nhật Ký Hành Trình Dimmr V</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue VI</t>
+          <t>Nhật Ký Hành Trình Dimmr VI</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Lahai-Roi Chương III: Thỏ Phản Chiếu Trong Bóng Râm</t>
+          <t>Chương III Lahai-Roi: Thỏ Ảnh Trong Sắc Tối</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Down Ghi chú</t>
+          <t>Nốt Trầm</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Up Ghi chú</t>
+          <t>Nốt Cao</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Steer Left</t>
+          <t>Rẽ trái</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Steer Right</t>
+          <t>Rẽ phải</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Màu Đỏ Rực Cháy Trong Ký Ức</t>
+          <t>Lửa Đỏ Trong Ký Ức</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Complete the prerequisite event</t>
+          <t>Hoàn thành sự kiện tiền đề trước</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Tương tác với Lynae sau khi hoàn thành sự kiện tiên quyết (16:00-18:00)</t>
+          <t>Tương tác với Lynae sau khi hoàn thành sự kiện tiền đề (16:00-18:00)</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại địa điểm chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại địa điểm chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại địa điểm chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại địa điểm chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Unlocked after 2026/03/20</t>
+          <t>Sẽ mở khóa sau 20/03/2026</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Unlocked after 2026/03/21</t>
+          <t>Sẽ mở khóa sau 21/03/2026</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả điều kiện tiền đề để mở khóa</t>
+          <t>Hoàn thành tất cả điều kiện tiên quyết để mở khóa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Complete 5 events to claim</t>
+          <t>Tham gia 5 sự kiện để nhận thưởng.</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Complete 10 events to claim</t>
+          <t>Hoàn thành 10 sự kiện để nhận thưởng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Complete 15 events to claim</t>
+          <t>Hoàn thành 15 sự kiện để nhận thưởng</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Complete 20 events to claim</t>
+          <t>Hoàn thành 20 sự kiện để nhận thưởng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Complete 26 events to claim</t>
+          <t>Hoàn thành 26 sự kiện để nhận thưởng</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Đã hoàn thành - I'll Show Bạn the Mech</t>
+          <t>Hoàn thành - Ta Sẽ Cho Ngươi Xem Mech</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Đã hoàn thành - Where the Iridescent Rain Falls</t>
+          <t>Hoàn thành - Nơi Mưa Ngũ Sắc Rơi</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Tấn Công Nhanh</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>"Homebound"</t>
+          <t>"Trở về nhà"</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Sigrika - Original Trang phục</t>
+          <t>Sigrika - Trang phục gốc</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Completed - Energy Supplement Trial Report</t>
+          <t>Hoàn thành - Báo cáo thử nghiệm bổ sung năng lượng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Completed - Environmental Variable Adjustment</t>
+          <t>Hoàn thành - Điều chỉnh biến số môi trường</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Completed - Abnormal Dopamine Secretion</t>
+          <t>Hoàn thành - Tiết dopamine bất thường</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Completed - Standardized Happiness</t>
+          <t>Hoàn thành - Hạnh Phúc Chuẩn Mực</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Completed - Sylph at Twilight</t>
+          <t>Hoàn thành - Sylph Trong Chạng Vạng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Completed - Waffle Therapy</t>
+          <t>Hoàn thành - Liệu Pháp Bánh Waffle</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Completed - Snack Deficit Syndrome</t>
+          <t>Hoàn thành - Hội Chứng Thiếu Hụt Đồ Ăn Vặt</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Completed - Immunodeficiency of Snacks</t>
+          <t>Hoàn thành - Hội Chứng Thiếu Đồ Ăn Vặt</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Completed - A Fluffy Prescription</t>
+          <t>Hoàn thành - Đơn thuốc mềm mại</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đã hoàn thành - The Heartbeat of Life</t>
+          <t>Hoàn thành - Nhịp Đập Của Sự Sống</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Completed - The Moored Boat</t>
+          <t>Hoàn thành - Con Thuyền Neo Đậu</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Completed - Creases on Paper</t>
+          <t>Hoàn thành - Nếp gấp trên giấy</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Completed - Ground Engravings</t>
+          <t>Hoàn thành - Những Dấu Khắc Trên Đất</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Completed - Imprints of Wings</t>
+          <t>Hoàn thành - Những Dấu Ấn Của Đôi Cánh</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Completed - Essence of Tranquility</t>
+          <t>Hoàn thành - Bản Chất Của Bình Yên</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Completed - The Happiness Spell</t>
+          <t>Hoàn thành - Phép Màu Hạnh Phúc</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Completed - "Festivals Don't Encore"</t>
+          <t>Hoàn thành - "Lễ hội không diễn lại"</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Completed - "Department of Engineering Repair Scene"</t>
+          <t>Hoàn thành - "Cảnh sửa chữa Bộ phận Kỹ thuật"</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Completed - "Life of a Resonator"</t>
+          <t>Hoàn thành - "Đời Resonator"</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Completed - "4½"</t>
+          <t>Hoàn thành - "4½"</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Completed - "Life is Beautiful"</t>
+          <t>Hoàn thành - "Cuộc sống thật đẹp"</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Frequency Cassette Recorder</t>
+          <t>Máy Ghi Âm Tần Số</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Nên hoàn thành Afterstory "The Flaming Red from Tomorrow" trước</t>
+          <t>Nên hoàn thành Afterstory "Lửa Đỏ Từ Ngày Mai" trước</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Complete Task: Ashinohara's "Lady Miko"</t>
+          <t>Hoàn thành Nhiệm vụ: "Quý cô Miko" của Ashinohara</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Complete Task: Special Response Force</t>
+          <t>Hoàn thành Nhiệm vụ: Lực lượng Đặc nhiệm</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Complete Task: The Rescued Researcher</t>
+          <t>Hoàn thành Nhiệm vụ: Nhà nghiên cứu được giải cứu</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ: The Film-Loving Ghost Miko</t>
+          <t>Hoàn thành Nhiệm vụ: Miko ma quỷ mê phim</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ: A Soliskin and Its Mysterious Friend</t>
+          <t>Hoàn thành Nhiệm vụ: Một mảnh da Solis và người bạn bí ẩn</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Complete Task: A Miko's Preferences</t>
+          <t>Hoàn thành Nhiệm vụ: Sở thích của Miko</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Complete Task: Platya's Gift</t>
+          <t>Hoàn thành Nhiệm vụ: Món quà của Platya</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Plush Dream</t>
+          <t>Giấc Mơ Nhung Lụa</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Mornye - Deluxe Trang phục</t>
+          <t>Chàooo - Trang phục Deluxe</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Dash (Left)</t>
+          <t>Tấn Công Nhanh (Trái)</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Dash (Right)</t>
+          <t>Tấn Công Nhanh (Phải)</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Duplicate Request ID</t>
+          <t>ID Yêu cầu trùng lặp</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Player data not found</t>
+          <t>Không tìm thấy dữ liệu của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Rewards đã được nhận</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Invalid status</t>
+          <t>Trạng thái không hợp lệ</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Đã mở khóa giai đoạn mới</t>
+          <t>Giai đoạn mới đã mở khóa</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Claimable Rewards</t>
+          <t>Phần thưởng có thể nhận</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bạn có một kiện hàng cần nhận</t>
+          <t>Cậu có một kiện hàng cần nhận</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Dimmr Traces</t>
+          <t>Dấu Vết Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks event ID mismatch</t>
+          <t>ID sự kiện Lahai-Roi Blocks không khớp</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Stage rewards already claimed</t>
+          <t>Đã nhận thưởng sân khấu.</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Stage already completed</t>
+          <t>Giai đoạn đã hoàn thành</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
